--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260825.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260825.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>10.94%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.39%</t>
+          <t>10.21%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.88%</t>
+          <t>7.90%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.49%</t>
+          <t>7.33%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.31%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>108,266</t>
+          <t>47,095</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.64%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>47,095</t>
+          <t>108,266</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1129,44 +1129,44 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>45,227</t>
+          <t>21,458</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,458</t>
+          <t>45,227</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1239,39 +1239,39 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>72,174</t>
+          <t>140,345</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>140,345</t>
+          <t>72,174</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,39 +1283,39 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>8,704</t>
+          <t>12,752</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>12,752</t>
+          <t>8,704</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,551</t>
+          <t>5,678</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,22 +1591,22 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>5,678</t>
+          <t>3,551</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>132,266,651</t>
+          <t>147,456,931</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
